--- a/баг-репорты.xlsx
+++ b/баг-репорты.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestProjectIntern_n1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8D5315-61F1-4892-8A9D-A8C7E0BF0CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B373E-84E4-48C5-B763-BEC36A2E6FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="4200" windowWidth="12405" windowHeight="11595" tabRatio="777" activeTab="3" xr2:uid="{43AB005C-4244-4F99-BE2A-3AA39DB38418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="777" activeTab="6" xr2:uid="{43AB005C-4244-4F99-BE2A-3AA39DB38418}"/>
   </bookViews>
   <sheets>
     <sheet name="Баг-репорт №1" sheetId="2" r:id="rId1"/>
     <sheet name="Баг-репорт №2" sheetId="3" r:id="rId2"/>
     <sheet name="Баг-репорт №3" sheetId="4" r:id="rId3"/>
     <sheet name="Баг-репорт №4" sheetId="5" r:id="rId4"/>
+    <sheet name="Баг-репорт №5" sheetId="6" r:id="rId5"/>
+    <sheet name="Баг-репорт №6" sheetId="8" r:id="rId6"/>
+    <sheet name="Баг-репорт №7" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="53">
   <si>
     <t>ID:</t>
   </si>
@@ -187,25 +190,65 @@
 </t>
   </si>
   <si>
-    <t>Нельзя переводить с копейками оругленных до сотых</t>
-  </si>
-  <si>
     <t>Минорный</t>
   </si>
   <si>
     <t>Низкий</t>
   </si>
   <si>
-    <t>1. В боди записываем в amount 0.5:var body = new List&lt;ParametrOperation&gt;()
+    <t>500 InternalServerError</t>
+  </si>
+  <si>
+    <t>Нельзя переводить с копейками</t>
+  </si>
+  <si>
+    <t>Нельзя пополнять счет с копейками</t>
+  </si>
+  <si>
+    <t>Можно переводить ноль на другой счет</t>
+  </si>
+  <si>
+    <t>Можно пополнять на ноль счет</t>
+  </si>
+  <si>
+    <t>1. В боди записываем в amount 0:var body = new List&lt;ParametrOperation&gt;()
 {
     new ParametrOperation {
         Identifier = "Account", Value = "[40875518618438343578]" },
     new ParametrOperation {
-        Identifier = "Amount", Value = ":0.5 },
+        Identifier = "Amount", Value = "0" },
 };</t>
   </si>
   <si>
-    <t>System.Text.Json.JsonException : The JSON value could not be converted to Operations.InfoOperation. Path: $ | LineNumber: 0 | BytePositionInLine: 53.</t>
+    <t>1. В боди записываем в amount 0:var body = new List&lt;ParametrOperation&gt;()
+{
+    new ParametrOperation {
+        Identifier = "SourceAccount", Value = "[40875518618438343578]" },new ParametrOperation {
+        Identifier = "ReceiverAccount", Value = "40830755020207104405" },
+};
+    new ParametrOperation {
+        Identifier = "Amount", Value = "0" },
+};</t>
+  </si>
+  <si>
+    <t>1. В боди записываем в amount 0.15:var body = new List&lt;ParametrOperation&gt;()
+{
+    new ParametrOperation {
+        Identifier = "SourceAccount", Value = "[40875518618438343578]" },new ParametrOperation {
+        Identifier = "ReceiverAccount", Value = "40830755020207104405" },
+};
+    new ParametrOperation {
+        Identifier = "Amount", Value = "0.15" },
+};</t>
+  </si>
+  <si>
+    <t>1. В боди записываем в amount 0.15:var body = new List&lt;ParametrOperation&gt;()
+{
+    new ParametrOperation {
+        Identifier = "Account", Value = "[40875518618438343578]" },
+    new ParametrOperation {
+        Identifier = "Amount", Value = "0.15" },
+};</t>
   </si>
 </sst>
 </file>
@@ -491,85 +534,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -581,28 +558,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -616,22 +575,106 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -802,22 +845,71 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>190498</xdr:colOff>
+      <xdr:colOff>347384</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>470646</xdr:rowOff>
+      <xdr:rowOff>448236</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>236791</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1920080</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>1509016</xdr:rowOff>
+      <xdr:rowOff>2115112</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
+        <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{584A0AE1-7438-4B96-9C7E-C39C2A71866E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93A8F5A2-B831-488B-8962-DCC3922D65E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2129119" y="12897971"/>
+          <a:ext cx="6178314" cy="1666876"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>189938</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>451036</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1762634</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2117912</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2616B7C9-D2A5-43D3-8F30-0E7BF71DB8F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -834,7 +926,105 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1971673" y="12900771"/>
-          <a:ext cx="14486193" cy="1038370"/>
+          <a:ext cx="6178314" cy="1666876"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>189938</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>451036</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1762634</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2117912</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A24490D1-0306-4017-964E-87859884B5B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1971113" y="12881161"/>
+          <a:ext cx="6173271" cy="1666876"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>347384</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>448236</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1920080</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2115112</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5EF878A-D7DE-49B7-9801-0D4DBC15C087}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2128559" y="12878361"/>
+          <a:ext cx="6173271" cy="1666876"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1147,44 +1337,44 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="40" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="40" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="40" customWidth="1"/>
-    <col min="5" max="7" width="9" style="40"/>
-    <col min="8" max="8" width="9" style="40" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="40"/>
+    <col min="1" max="1" width="26.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" style="12" customWidth="1"/>
+    <col min="5" max="7" width="9" style="12"/>
+    <col min="8" max="8" width="9" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="43">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1201,162 +1391,170 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="14" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="43" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4" ht="36" customHeight="1">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="43" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="43"/>
+      <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="17" t="s">
+      <c r="C12" s="32"/>
+      <c r="D12" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="20"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="29"/>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="20"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="29"/>
     </row>
     <row r="15" spans="1:4" ht="30.75" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="24"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" spans="1:4" ht="48.75" customHeight="1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="91.5" customHeight="1">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="48" customHeight="1">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" ht="195.75" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="40" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="40" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="40" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="12" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="B17:C18"/>
     <mergeCell ref="D17:D18"/>
     <mergeCell ref="B20:D20"/>
@@ -1367,14 +1565,6 @@
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="B12:C15"/>
     <mergeCell ref="D12:D15"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{838CB8D7-0030-41AB-A965-2C4AA27EC5DD}"/>
@@ -1391,44 +1581,44 @@
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="40" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="40" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="57.5703125" style="40" customWidth="1"/>
-    <col min="5" max="7" width="9" style="40"/>
-    <col min="8" max="8" width="9" style="40" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="40"/>
+    <col min="1" max="1" width="26.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" style="12" customWidth="1"/>
+    <col min="5" max="7" width="9" style="12"/>
+    <col min="8" max="8" width="9" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="43">
         <v>2</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1445,160 +1635,882 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="43" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4" ht="36" customHeight="1">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="43" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="43"/>
+      <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="17" t="s">
+      <c r="C12" s="32"/>
+      <c r="D12" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="20"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="29"/>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="20"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="29"/>
     </row>
     <row r="15" spans="1:4" ht="30.75" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="24"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" spans="1:4" ht="48.75" customHeight="1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="231.75" customHeight="1">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="126" customHeight="1">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" ht="195.75" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="40" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="40" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="40" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="12" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:C15"/>
+    <mergeCell ref="D12:D15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C7FDAB-26C6-4241-BB7D-5F7C2E20F2A6}">
+  <sheetPr codeName="Лист4"/>
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" style="12" customWidth="1"/>
+    <col min="5" max="7" width="9" style="12"/>
+    <col min="8" max="8" width="9" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43">
+        <v>3</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4" ht="36" customHeight="1">
+      <c r="A11" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="27"/>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="29"/>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="29"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="29"/>
+    </row>
+    <row r="15" spans="1:4" ht="30.75" customHeight="1">
+      <c r="A15" s="30"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="30"/>
+    </row>
+    <row r="16" spans="1:4" ht="48.75" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" ht="231.75" customHeight="1">
+      <c r="A17" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="126" customHeight="1">
+      <c r="A18" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" ht="195.75" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="12" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:C15"/>
+    <mergeCell ref="D12:D15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F0E08B-43CC-4A82-A411-8018AA14B318}">
+  <sheetPr codeName="Лист5"/>
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" style="12" customWidth="1"/>
+    <col min="5" max="7" width="9" style="12"/>
+    <col min="8" max="8" width="9" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43">
+        <v>4</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4" ht="36" customHeight="1">
+      <c r="A11" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="27"/>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="29"/>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="29"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="29"/>
+    </row>
+    <row r="15" spans="1:4" ht="30.75" customHeight="1">
+      <c r="A15" s="30"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="30"/>
+    </row>
+    <row r="16" spans="1:4" ht="48.75" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" ht="231.75" customHeight="1">
+      <c r="A17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="126" customHeight="1">
+      <c r="A18" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" ht="195.75" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="12" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:C15"/>
+    <mergeCell ref="D12:D15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A2864FD-5BFA-4845-AD5A-85C8A44C062E}">
+  <dimension ref="A1:D69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="26.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" style="12" customWidth="1"/>
+    <col min="5" max="7" width="9" style="12"/>
+    <col min="8" max="8" width="9" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43">
+        <v>5</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
+    </row>
+    <row r="2" spans="1:4" ht="49.5" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+    </row>
+    <row r="3" spans="1:4" ht="36" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
+    </row>
+    <row r="4" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="75.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="29.1" customHeight="1">
+      <c r="A6" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
+    </row>
+    <row r="8" spans="1:4" ht="26.1" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" spans="1:4" ht="24.95" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+    </row>
+    <row r="10" spans="1:4" ht="35.1" customHeight="1">
+      <c r="A10" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4" ht="36" customHeight="1">
+      <c r="A11" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="27"/>
+    </row>
+    <row r="12" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A12" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" customHeight="1">
+      <c r="A13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="29"/>
+    </row>
+    <row r="14" spans="1:4" ht="27" customHeight="1">
+      <c r="A14" s="29"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="29"/>
+    </row>
+    <row r="15" spans="1:4" ht="30.75" customHeight="1">
+      <c r="A15" s="30"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="30"/>
+    </row>
+    <row r="16" spans="1:4" ht="48.75" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" ht="231.75" customHeight="1">
+      <c r="A17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="126" customHeight="1">
+      <c r="A18" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+    </row>
+    <row r="20" spans="1:4" ht="195.75" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
+    <row r="67" s="12" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B17:C18"/>
@@ -1626,50 +2538,49 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C7FDAB-26C6-4241-BB7D-5F7C2E20F2A6}">
-  <sheetPr codeName="Лист4"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1372AC9B-6B03-40E0-8CD1-2C960BEB6FF2}">
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="40" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="40" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="57.5703125" style="40" customWidth="1"/>
-    <col min="5" max="7" width="9" style="40"/>
-    <col min="8" max="8" width="9" style="40" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="40"/>
+    <col min="1" max="1" width="26.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" style="12" customWidth="1"/>
+    <col min="5" max="7" width="9" style="12"/>
+    <col min="8" max="8" width="9" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
-        <v>3</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="43">
+        <v>6</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="B2" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1686,160 +2597,160 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="43"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4" ht="36" customHeight="1">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="43"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="17" t="s">
+      <c r="C12" s="32"/>
+      <c r="D12" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="20"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="29"/>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="20"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="29"/>
     </row>
     <row r="15" spans="1:4" ht="30.75" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="24"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" spans="1:4" ht="48.75" customHeight="1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="231.75" customHeight="1">
-      <c r="A17" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="45" t="s">
+      <c r="A17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="126" customHeight="1">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" ht="195.75" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="40" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="40" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="40" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="12" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B17:C18"/>
@@ -1867,50 +2778,49 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F0E08B-43CC-4A82-A411-8018AA14B318}">
-  <sheetPr codeName="Лист5"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{688D2D00-7C99-46AF-B69F-B7D264A03B6D}">
   <dimension ref="A1:D69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="40" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="40" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="57.5703125" style="40" customWidth="1"/>
-    <col min="5" max="7" width="9" style="40"/>
-    <col min="8" max="8" width="9" style="40" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="40"/>
+    <col min="1" max="1" width="26.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" style="12" customWidth="1"/>
+    <col min="5" max="7" width="9" style="12"/>
+    <col min="8" max="8" width="9" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
-        <v>3</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="43">
+        <v>4</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:4" ht="49.5" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="B2" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="45"/>
     </row>
     <row r="4" spans="1:4" ht="37.5" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -1927,160 +2837,160 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="75.75" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="49"/>
     </row>
     <row r="7" spans="1:4" ht="39.75" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
     </row>
     <row r="8" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
     </row>
     <row r="9" spans="1:4" ht="24.95" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
     </row>
     <row r="10" spans="1:4" ht="35.1" customHeight="1">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="43" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4" ht="36" customHeight="1">
+      <c r="A11" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="43"/>
-    </row>
-    <row r="11" spans="1:4" ht="36" customHeight="1">
-      <c r="A11" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="43"/>
+      <c r="D11" s="27"/>
     </row>
     <row r="12" spans="1:4" ht="28.5" customHeight="1">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="17" t="s">
+      <c r="C12" s="32"/>
+      <c r="D12" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="27" customHeight="1">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="20"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="29"/>
     </row>
     <row r="14" spans="1:4" ht="27" customHeight="1">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="20"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="29"/>
     </row>
     <row r="15" spans="1:4" ht="30.75" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="24"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" spans="1:4" ht="48.75" customHeight="1">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="231.75" customHeight="1">
-      <c r="A17" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37" t="s">
+      <c r="A17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>38</v>
       </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="126" customHeight="1">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20" spans="1:4" ht="195.75" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="24"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
     </row>
     <row r="22" spans="1:4" ht="57.75" customHeight="1"/>
     <row r="23" spans="1:4" ht="47.25" customHeight="1"/>
-    <row r="67" s="40" customFormat="1" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" s="40" customFormat="1" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" s="40" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="67" s="12" customFormat="1" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" s="12" customFormat="1" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B17:C18"/>

--- a/баг-репорты.xlsx
+++ b/баг-репорты.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestProjectIntern_n1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B373E-84E4-48C5-B763-BEC36A2E6FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9FC123-788C-47B8-8666-F31E4E8F6B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="777" activeTab="6" xr2:uid="{43AB005C-4244-4F99-BE2A-3AA39DB38418}"/>
+    <workbookView minimized="1" xWindow="13740" yWindow="3885" windowWidth="12405" windowHeight="11595" tabRatio="777" activeTab="6" xr2:uid="{43AB005C-4244-4F99-BE2A-3AA39DB38418}"/>
   </bookViews>
   <sheets>
     <sheet name="Баг-репорт №1" sheetId="2" r:id="rId1"/>
